--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17588,7 +17588,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17588,7 +17588,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20288,16 +20288,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="O103" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.284609467338262</v>
+        <v>0.6225832098024481</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -20450,10 +20450,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="O104" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>757</v>
+        <v>776</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20765,6 +20765,408 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20798,7 +21200,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -20881,7 +21283,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -20891,7 +21293,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -20911,7 +21313,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.04440596913918363</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1303,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1448,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1856,9 +1844,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2108,7 +2093,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2258,9 +2243,6 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2510,7 +2492,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2660,9 +2642,6 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2912,7 +2891,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3062,9 +3041,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3314,7 +3290,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3461,9 +3437,6 @@
       <c r="O16" t="n">
         <v>3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.03330447685438772</v>
       </c>
@@ -3609,9 +3582,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4008,9 +3978,6 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4260,7 +4227,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4407,9 +4374,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4555,9 +4519,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4954,9 +4915,6 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5206,7 +5164,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5356,9 +5314,6 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5608,7 +5563,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -5758,9 +5713,6 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6010,7 +5962,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6157,9 +6109,6 @@
       <c r="O30" t="n">
         <v>11</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -6305,9 +6254,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6704,9 +6650,6 @@
       <c r="P33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6956,7 +6899,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7103,9 +7046,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7251,9 +7191,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -7650,9 +7587,6 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7902,7 +7836,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8052,9 +7986,6 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8304,7 +8235,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8454,9 +8385,6 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8706,7 +8634,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8856,9 +8784,6 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9108,7 +9033,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9255,9 +9180,6 @@
       <c r="O46" t="n">
         <v>32</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.355247753113469</v>
       </c>
@@ -9403,9 +9325,6 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -9799,9 +9718,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9947,9 +9863,6 @@
       <c r="O50" t="n">
         <v>5</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -10346,9 +10259,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10598,7 +10508,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10748,9 +10658,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11000,7 +10907,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11150,9 +11057,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11402,7 +11306,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11552,9 +11456,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11804,7 +11705,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -11951,9 +11852,6 @@
       <c r="O60" t="n">
         <v>68</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.7549014753661216</v>
       </c>
@@ -12099,9 +11997,6 @@
       <c r="O61" t="n">
         <v>32</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.569218934676524</v>
       </c>
@@ -12495,9 +12390,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12643,9 +12535,6 @@
       <c r="O64" t="n">
         <v>23</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.214932249850517</v>
       </c>
@@ -13042,9 +12931,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13294,7 +13180,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13444,9 +13330,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13696,7 +13579,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13846,9 +13729,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14098,7 +13978,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14248,9 +14128,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -14500,7 +14377,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -14650,9 +14527,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14902,7 +14776,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15049,9 +14923,6 @@
       <c r="O76" t="n">
         <v>107</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>1.187859674473162</v>
       </c>
@@ -15197,9 +15068,6 @@
       <c r="O77" t="n">
         <v>104</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>1.849961537698703</v>
       </c>
@@ -15593,9 +15461,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15741,9 +15606,6 @@
       <c r="O80" t="n">
         <v>92</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.8597289994020678</v>
       </c>
@@ -16140,9 +16002,6 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -16392,7 +16251,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16542,9 +16401,6 @@
       <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -16794,7 +16650,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -16944,9 +16800,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -17196,7 +17049,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17346,9 +17199,6 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -17598,7 +17448,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -17745,9 +17595,6 @@
       <c r="O90" t="n">
         <v>100</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.778809170864138</v>
       </c>
@@ -18141,9 +17988,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -18284,16 +18128,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O93" t="n">
-        <v>157</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="R93" t="n">
-        <v>1.467146227240485</v>
+        <v>1.457801346812202</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -18446,10 +18287,10 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O94" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -18688,9 +18529,6 @@
       <c r="P95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -18940,7 +18778,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -19090,9 +18928,6 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -19342,7 +19177,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -19492,9 +19327,6 @@
       <c r="P99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -19744,7 +19576,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -19894,9 +19726,6 @@
       <c r="P101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -20146,7 +19975,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -20288,16 +20117,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O103" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R103" t="n">
-        <v>0.6225832098024481</v>
+        <v>0.7115236683456551</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -20450,10 +20276,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O104" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -20689,9 +20515,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -20840,9 +20663,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -21092,7 +20912,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21345,7 +21165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20117,13 +20117,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O103" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R103" t="n">
-        <v>0.7115236683456551</v>
+        <v>0.7293117600542963</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -20276,10 +20276,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O104" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20117,13 +20117,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="O103" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="R103" t="n">
-        <v>0.7293117600542963</v>
+        <v>0.8716164937234273</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -20276,10 +20276,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="O104" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>781</v>
+        <v>789</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20117,13 +20117,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O103" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="R103" t="n">
-        <v>0.8716164937234273</v>
+        <v>0.9427688605579929</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -20276,10 +20276,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O104" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -20982,6 +20982,405 @@
         </is>
       </c>
       <c r="BC107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -21020,7 +21419,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -21103,7 +21502,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -21113,7 +21512,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -21133,7 +21532,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -21165,7 +21564,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -9175,13 +9175,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R46" t="n">
-        <v>0.355247753113469</v>
+        <v>0.3774507376830608</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -11847,13 +11847,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O60" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R60" t="n">
-        <v>0.7549014753661216</v>
+        <v>0.7437999830813258</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -14918,13 +14918,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="O76" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="R76" t="n">
-        <v>1.187859674473162</v>
+        <v>1.365483551029897</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -17551,12 +17551,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -17590,95 +17590,81 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O90" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R90" t="n">
-        <v>1.778809170864138</v>
+        <v>1.121250720764387</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_708</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_708</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -17705,7 +17691,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17754,98 +17740,23 @@
       <c r="O91" t="n">
         <v>100</v>
       </c>
+      <c r="R91" t="n">
+        <v>1.778809170864138</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_708</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>TBE (tick borne encephalitis)</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN91" t="b">
-        <v>1</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -17939,17 +17850,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -17983,81 +17894,170 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18089,12 +18089,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -18128,95 +18128,81 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.457801346812202</v>
+        <v>0</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TBE</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TBE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18243,7 +18229,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18287,103 +18273,28 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O94" t="n">
-        <v>156</v>
+        <v>155</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.448456466383919</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TBE</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>TBE</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD94" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG94" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM TBE disease category.</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN94" t="b">
-        <v>1</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -18477,17 +18388,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -18512,7 +18423,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -18521,31 +18432,103 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>155</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>TBE</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM TBE disease category.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -18564,7 +18547,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -18577,42 +18560,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18639,7 +18622,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18691,98 +18674,23 @@
       <c r="P96" t="n">
         <v>0</v>
       </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN96" t="b">
-        <v>1</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -18876,7 +18784,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18911,7 +18819,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -18928,23 +18836,98 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -19038,7 +19021,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19090,98 +19073,23 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -19275,7 +19183,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19310,7 +19218,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -19319,31 +19227,106 @@
         </is>
       </c>
       <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
         <v>1</v>
-      </c>
-      <c r="O99" t="n">
-        <v>1</v>
-      </c>
-      <c r="P99" t="n">
-        <v>1</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -19437,7 +19420,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19489,98 +19472,23 @@
       <c r="P100" t="n">
         <v>1</v>
       </c>
+      <c r="R100" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -19674,7 +19582,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19709,7 +19617,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -19718,31 +19626,106 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -19836,7 +19819,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -19888,98 +19871,23 @@
       <c r="P102" t="n">
         <v>0</v>
       </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN102" t="b">
-        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -20073,17 +19981,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -20108,37 +20016,115 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>53</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0.9427688605579929</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -20152,12 +20138,12 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -20165,47 +20151,47 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20232,7 +20218,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -20276,103 +20262,28 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O104" t="n">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="R104" t="n">
+        <v>1.067285502518482</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_708</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>TBE (tick borne encephalitis)</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN104" t="b">
-        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -20466,17 +20377,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -20510,81 +20421,170 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20616,12 +20616,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -20660,9 +20660,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20671,82 +20668,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20773,7 +20756,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -20825,98 +20808,23 @@
       <c r="P107" t="n">
         <v>0</v>
       </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD107" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE107" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG107" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN107" t="b">
-        <v>1</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -21010,7 +20918,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -21045,7 +20953,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -21062,23 +20970,98 @@
       <c r="P108" t="n">
         <v>0</v>
       </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN108" t="b">
+        <v>1</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -21172,7 +21155,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -21224,98 +21207,23 @@
       <c r="P109" t="n">
         <v>0</v>
       </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN109" t="b">
-        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -21381,6 +21289,243 @@
         </is>
       </c>
       <c r="BC109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -21502,7 +21647,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -21512,7 +21657,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -21564,7 +21709,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>793</v>
+        <v>917</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20262,13 +20262,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O104" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R104" t="n">
-        <v>1.067285502518482</v>
+        <v>1.102861685935765</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20421,10 +20421,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O105" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20262,13 +20262,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O104" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="R104" t="n">
-        <v>1.102861685935765</v>
+        <v>1.191802144478972</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20421,10 +20421,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O105" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>919</v>
+        <v>924</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20262,13 +20262,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="O104" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="R104" t="n">
-        <v>1.191802144478972</v>
+        <v>1.511987795234517</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20421,10 +20421,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="O105" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21526,6 +21526,405 @@
         </is>
       </c>
       <c r="BC110" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -21564,7 +21963,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -21647,7 +22046,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -21657,7 +22056,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -21677,7 +22076,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -21709,7 +22108,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>924</v>
+        <v>942</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20262,13 +20262,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O104" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R104" t="n">
-        <v>1.511987795234517</v>
+        <v>1.529775886943158</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20421,10 +20421,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O105" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22108,7 +22108,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -943,17 +943,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1169,7 +1174,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1177,17 +1182,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1473,7 +1483,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1491,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1722,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1730,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2083,7 +2103,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2482,7 +2502,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2881,7 +2901,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3300,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3607,7 +3627,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3615,17 +3635,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3841,7 +3866,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3849,17 +3874,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4217,7 +4247,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4544,7 +4574,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4552,17 +4582,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4778,7 +4813,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4786,17 +4821,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5154,7 +5194,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5553,7 +5593,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5952,7 +5992,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6279,7 +6319,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6287,17 +6327,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6513,7 +6558,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6521,17 +6566,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6889,7 +6939,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7216,7 +7266,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7224,17 +7274,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7450,7 +7505,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7458,17 +7513,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7826,7 +7886,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8225,7 +8285,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8624,7 +8684,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9023,7 +9083,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9350,7 +9410,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9358,17 +9418,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9584,7 +9649,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9592,17 +9657,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9888,7 +9958,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -9896,17 +9966,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10122,7 +10197,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10130,17 +10205,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10498,7 +10578,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10897,7 +10977,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11296,7 +11376,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11695,7 +11775,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12022,7 +12102,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12030,17 +12110,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12256,7 +12341,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12264,17 +12349,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12560,7 +12650,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12568,17 +12658,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -12794,7 +12889,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -12802,17 +12897,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13170,7 +13270,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13569,7 +13669,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13968,7 +14068,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14367,7 +14467,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14766,7 +14866,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15093,7 +15193,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -15101,17 +15201,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -15327,7 +15432,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -15335,17 +15440,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -15631,7 +15741,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -15639,17 +15749,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -15865,7 +15980,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -15873,17 +15988,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -16241,7 +16361,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16640,7 +16760,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17039,7 +17159,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17438,7 +17558,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17765,7 +17885,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -17773,17 +17893,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS91" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -17999,7 +18124,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -18007,17 +18132,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS92" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -18303,7 +18433,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -18311,17 +18441,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS94" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -18537,7 +18672,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -18545,17 +18680,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS95" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -18913,7 +19053,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19312,7 +19452,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19711,7 +19851,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20110,7 +20250,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20292,7 +20432,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -20300,17 +20440,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -20526,7 +20671,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -20534,17 +20679,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -21047,7 +21197,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21446,7 +21596,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21845,7 +21995,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -18403,13 +18403,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O94" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R94" t="n">
-        <v>1.448456466383919</v>
+        <v>1.439111585955635</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18567,10 +18567,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O95" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -20402,13 +20402,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="O104" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="R104" t="n">
-        <v>1.529775886943158</v>
+        <v>1.725444895738213</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20566,10 +20566,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="O105" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -22077,6 +22077,953 @@
       <c r="BC112" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22113,7 +23060,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -22196,7 +23143,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -22206,7 +23153,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -22226,7 +23173,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -22258,7 +23205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>943</v>
+        <v>954</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20402,13 +20402,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O104" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R104" t="n">
-        <v>1.725444895738213</v>
+        <v>1.761021079155496</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20566,10 +20566,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O105" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -22546,13 +22546,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="16">
